--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/10,08,26 Останкино КИ и ЗПФ/машина САП 16,08 Донецк_ПРС_Малахутин_БарановаКарпова КИ/Заказ ЛП_опт Баранова, Карлова 12.08 Донецк.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/10,08,26 Останкино КИ и ЗПФ/машина САП 16,08 Донецк_ПРС_Малахутин_БарановаКарпова КИ/Заказ ЛП_опт Баранова, Карлова 12.08 Донецк.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uaer4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\10,08,26 Останкино КИ и ЗПФ\машина САП 16,08 Донецк_ПРС_Малахутин_БарановаКарпова КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94ECF5DF-2837-4261-9C65-EF93F2C4E96A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F73D210-47E6-4FBF-A558-41561E48814F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6238,7 +6238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BO1687"/>
@@ -6462,7 +6462,7 @@
       <c r="BN9" s="120"/>
       <c r="BO9" s="120"/>
     </row>
-    <row r="10" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
       <c r="B10" s="43" t="s">
         <v>18</v>
@@ -6476,7 +6476,7 @@
       <c r="I10" s="43"/>
       <c r="J10" s="44"/>
     </row>
-    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="str">
         <f>RIGHT(D11,4)</f>
         <v>4561</v>
@@ -6563,7 +6563,7 @@
       <c r="BN11" s="121"/>
       <c r="BO11" s="121"/>
     </row>
-    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="145" t="str">
         <f t="shared" ref="A12:A74" si="1">RIGHT(D12,4)</f>
         <v>7536</v>
@@ -6652,7 +6652,7 @@
       <c r="BN12" s="121"/>
       <c r="BO12" s="121"/>
     </row>
-    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="str">
         <f t="shared" si="1"/>
         <v>5851</v>
@@ -6830,7 +6830,7 @@
       <c r="BN14" s="121"/>
       <c r="BO14" s="121"/>
     </row>
-    <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="str">
         <f t="shared" si="1"/>
         <v>4574</v>
@@ -7054,7 +7054,7 @@
       <c r="J18" s="29"/>
       <c r="L18" s="122"/>
     </row>
-    <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6861</v>
@@ -7085,7 +7085,7 @@
       <c r="J19" s="29"/>
       <c r="L19" s="122"/>
     </row>
-    <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6862</v>
@@ -7116,7 +7116,7 @@
       <c r="J20" s="29"/>
       <c r="L20" s="122"/>
     </row>
-    <row r="21" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="145" t="str">
         <f t="shared" si="1"/>
         <v>7539</v>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L21" s="122"/>
     </row>
-    <row r="22" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7334</v>
@@ -7180,7 +7180,7 @@
       <c r="J22" s="29"/>
       <c r="L22" s="122"/>
     </row>
-    <row r="23" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6325</v>
@@ -7211,7 +7211,7 @@
       <c r="J23" s="29"/>
       <c r="L23" s="122"/>
     </row>
-    <row r="24" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="str">
         <f t="shared" si="1"/>
         <v>8014</v>
@@ -7298,7 +7298,7 @@
       <c r="BN24" s="122"/>
       <c r="BO24" s="122"/>
     </row>
-    <row r="25" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="145">
         <v>7632</v>
       </c>
@@ -7386,7 +7386,7 @@
       <c r="BN25" s="122"/>
       <c r="BO25" s="122"/>
     </row>
-    <row r="26" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="145" t="str">
         <f t="shared" si="1"/>
         <v>7523</v>
@@ -7475,7 +7475,7 @@
       <c r="BN26" s="122"/>
       <c r="BO26" s="122"/>
     </row>
-    <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6340</v>
@@ -7506,7 +7506,7 @@
       <c r="J27" s="29"/>
       <c r="L27" s="122"/>
     </row>
-    <row r="28" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6341</v>
@@ -7537,7 +7537,7 @@
       <c r="J28" s="61"/>
       <c r="L28" s="122"/>
     </row>
-    <row r="29" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6333</v>
@@ -7568,7 +7568,7 @@
       <c r="J29" s="61"/>
       <c r="L29" s="122"/>
     </row>
-    <row r="30" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6392</v>
@@ -7599,7 +7599,7 @@
       <c r="J30" s="61"/>
       <c r="L30" s="122"/>
     </row>
-    <row r="31" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7343</v>
@@ -7630,7 +7630,7 @@
       <c r="J31" s="29"/>
       <c r="L31" s="122"/>
     </row>
-    <row r="32" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6797</v>
@@ -7717,7 +7717,7 @@
       <c r="BN32" s="122"/>
       <c r="BO32" s="122"/>
     </row>
-    <row r="33" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7231</v>
@@ -7804,7 +7804,7 @@
       <c r="BN33" s="122"/>
       <c r="BO33" s="122"/>
     </row>
-    <row r="34" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="48" t="s">
         <v>104</v>
       </c>
@@ -7821,7 +7821,7 @@
       <c r="J34" s="44"/>
       <c r="L34" s="122"/>
     </row>
-    <row r="35" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6767</v>
@@ -7908,7 +7908,7 @@
       <c r="BN35" s="122"/>
       <c r="BO35" s="122"/>
     </row>
-    <row r="36" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6761</v>
@@ -7995,7 +7995,7 @@
       <c r="BN36" s="122"/>
       <c r="BO36" s="122"/>
     </row>
-    <row r="37" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6764</v>
@@ -8082,7 +8082,7 @@
       <c r="BN37" s="122"/>
       <c r="BO37" s="122"/>
     </row>
-    <row r="38" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6254</v>
@@ -8169,7 +8169,7 @@
       <c r="BN38" s="122"/>
       <c r="BO38" s="122"/>
     </row>
-    <row r="39" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7075</v>
@@ -8256,7 +8256,7 @@
       <c r="BN39" s="122"/>
       <c r="BO39" s="122"/>
     </row>
-    <row r="40" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7083</v>
@@ -8521,7 +8521,7 @@
       <c r="BN42" s="122"/>
       <c r="BO42" s="122"/>
     </row>
-    <row r="43" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7076</v>
@@ -8608,7 +8608,7 @@
       <c r="BN43" s="122"/>
       <c r="BO43" s="122"/>
     </row>
-    <row r="44" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7271</v>
@@ -8784,7 +8784,7 @@
       <c r="BN45" s="122"/>
       <c r="BO45" s="122"/>
     </row>
-    <row r="46" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6661</v>
@@ -8871,7 +8871,7 @@
       <c r="BN46" s="122"/>
       <c r="BO46" s="122"/>
     </row>
-    <row r="47" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6759</v>
@@ -8958,7 +8958,7 @@
       <c r="BN47" s="122"/>
       <c r="BO47" s="122"/>
     </row>
-    <row r="48" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6762</v>
@@ -9045,7 +9045,7 @@
       <c r="BN48" s="122"/>
       <c r="BO48" s="122"/>
     </row>
-    <row r="49" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6765</v>
@@ -9132,7 +9132,7 @@
       <c r="BN49" s="122"/>
       <c r="BO49" s="122"/>
     </row>
-    <row r="50" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7074</v>
@@ -9219,7 +9219,7 @@
       <c r="BN50" s="122"/>
       <c r="BO50" s="122"/>
     </row>
-    <row r="51" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7123</v>
@@ -9306,7 +9306,7 @@
       <c r="BN51" s="122"/>
       <c r="BO51" s="122"/>
     </row>
-    <row r="52" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="58" t="str">
         <f t="shared" si="1"/>
         <v>5819</v>
@@ -9393,7 +9393,7 @@
       <c r="BN52" s="122"/>
       <c r="BO52" s="122"/>
     </row>
-    <row r="53" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6475</v>
@@ -9480,7 +9480,7 @@
       <c r="BN53" s="122"/>
       <c r="BO53" s="122"/>
     </row>
-    <row r="54" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7284</v>
@@ -9567,7 +9567,7 @@
       <c r="BN54" s="122"/>
       <c r="BO54" s="122"/>
     </row>
-    <row r="55" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7601</v>
@@ -9654,7 +9654,7 @@
       <c r="BN55" s="122"/>
       <c r="BO55" s="122"/>
     </row>
-    <row r="56" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7461</v>
@@ -9743,7 +9743,7 @@
       <c r="BN56" s="122"/>
       <c r="BO56" s="122"/>
     </row>
-    <row r="57" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7371</v>
@@ -9830,7 +9830,7 @@
       <c r="BN57" s="122"/>
       <c r="BO57" s="122"/>
     </row>
-    <row r="58" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6837</v>
@@ -9917,7 +9917,7 @@
       <c r="BN58" s="122"/>
       <c r="BO58" s="122"/>
     </row>
-    <row r="59" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7080</v>
@@ -9948,7 +9948,7 @@
       <c r="J59" s="29"/>
       <c r="L59" s="122"/>
     </row>
-    <row r="60" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6724</v>
@@ -10012,7 +10012,7 @@
       <c r="J61" s="29"/>
       <c r="L61" s="122"/>
     </row>
-    <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6713</v>
@@ -10043,7 +10043,7 @@
       <c r="J62" s="29"/>
       <c r="L62" s="122"/>
     </row>
-    <row r="63" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7255</v>
@@ -10074,7 +10074,7 @@
       <c r="J63" s="29"/>
       <c r="L63" s="122"/>
     </row>
-    <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6602</v>
@@ -10105,7 +10105,7 @@
       <c r="J64" s="29"/>
       <c r="L64" s="122"/>
     </row>
-    <row r="65" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7073</v>
@@ -10136,7 +10136,7 @@
       <c r="J65" s="29"/>
       <c r="L65" s="122"/>
     </row>
-    <row r="66" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7276</v>
@@ -10200,7 +10200,7 @@
       <c r="J67" s="29"/>
       <c r="L67" s="122"/>
     </row>
-    <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7385</v>
@@ -10231,7 +10231,7 @@
       <c r="J68" s="29"/>
       <c r="L68" s="122"/>
     </row>
-    <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7044</v>
@@ -10262,7 +10262,7 @@
       <c r="J69" s="29"/>
       <c r="L69" s="122"/>
     </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="58" t="str">
         <f t="shared" si="1"/>
         <v>7460</v>
@@ -10293,7 +10293,7 @@
       <c r="J70" s="29"/>
       <c r="L70" s="122"/>
     </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="48" t="s">
         <v>104</v>
       </c>
@@ -10310,7 +10310,7 @@
       <c r="J71" s="44"/>
       <c r="L71" s="122"/>
     </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A72" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6527</v>
@@ -10341,7 +10341,7 @@
       <c r="J72" s="61"/>
       <c r="L72" s="122"/>
     </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6550</v>
@@ -10372,7 +10372,7 @@
       <c r="J73" s="29"/>
       <c r="L73" s="122"/>
     </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="58" t="str">
         <f t="shared" si="1"/>
         <v>6549</v>
@@ -10403,7 +10403,7 @@
       <c r="J74" s="29"/>
       <c r="L74" s="122"/>
     </row>
-    <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="58" t="str">
         <f t="shared" ref="A75:A78" si="9">RIGHT(D75,4)</f>
         <v>7001</v>
@@ -10434,7 +10434,7 @@
       <c r="J75" s="29"/>
       <c r="L75" s="122"/>
     </row>
-    <row r="76" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="58" t="str">
         <f t="shared" si="9"/>
         <v>6608</v>
@@ -10465,7 +10465,7 @@
       <c r="J76" s="29"/>
       <c r="L76" s="122"/>
     </row>
-    <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="58" t="str">
         <f t="shared" si="9"/>
         <v>7059</v>
@@ -10496,7 +10496,7 @@
       <c r="J77" s="29"/>
       <c r="L77" s="122"/>
     </row>
-    <row r="78" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="58" t="str">
         <f t="shared" si="9"/>
         <v>6609</v>
@@ -10527,7 +10527,7 @@
       <c r="J78" s="29"/>
       <c r="L78" s="122"/>
     </row>
-    <row r="79" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="48" t="s">
         <v>104</v>
       </c>
@@ -10544,7 +10544,7 @@
       <c r="J79" s="44"/>
       <c r="L79" s="122"/>
     </row>
-    <row r="80" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A80" s="145" t="str">
         <f t="shared" ref="A80:A102" si="11">RIGHT(D80,4)</f>
         <v>7564</v>
@@ -10577,7 +10577,7 @@
       </c>
       <c r="L80" s="122"/>
     </row>
-    <row r="81" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7133</v>
@@ -10608,7 +10608,7 @@
       <c r="J81" s="61"/>
       <c r="L81" s="122"/>
     </row>
-    <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="58" t="str">
         <f t="shared" si="11"/>
         <v>6946</v>
@@ -10639,7 +10639,7 @@
       <c r="J82" s="29"/>
       <c r="L82" s="122"/>
     </row>
-    <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7132</v>
@@ -10703,7 +10703,7 @@
       <c r="J84" s="61"/>
       <c r="L84" s="122"/>
     </row>
-    <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7149</v>
@@ -10734,7 +10734,7 @@
       <c r="J85" s="61"/>
       <c r="L85" s="122"/>
     </row>
-    <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7157</v>
@@ -10798,7 +10798,7 @@
       <c r="J87" s="61"/>
       <c r="L87" s="122"/>
     </row>
-    <row r="88" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="145" t="str">
         <f t="shared" si="11"/>
         <v>7603</v>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="L88" s="122"/>
     </row>
-    <row r="89" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="58" t="str">
         <f t="shared" si="11"/>
         <v>6807</v>
@@ -10862,7 +10862,7 @@
       <c r="J89" s="29"/>
       <c r="L89" s="122"/>
     </row>
-    <row r="90" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="58" t="str">
         <f t="shared" si="11"/>
         <v>6787</v>
@@ -10893,7 +10893,7 @@
       <c r="J90" s="29"/>
       <c r="L90" s="122"/>
     </row>
-    <row r="91" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="58" t="str">
         <f t="shared" si="11"/>
         <v>6697</v>
@@ -10926,7 +10926,7 @@
       <c r="J91" s="29"/>
       <c r="L91" s="122"/>
     </row>
-    <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7169</v>
@@ -10957,7 +10957,7 @@
       <c r="J92" s="29"/>
       <c r="L92" s="122"/>
     </row>
-    <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7233</v>
@@ -10988,7 +10988,7 @@
       <c r="J93" s="29"/>
       <c r="L93" s="122"/>
     </row>
-    <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7236</v>
@@ -11019,7 +11019,7 @@
       <c r="J94" s="50"/>
       <c r="L94" s="122"/>
     </row>
-    <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7177</v>
@@ -11050,7 +11050,7 @@
       <c r="J95" s="50"/>
       <c r="L95" s="122"/>
     </row>
-    <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7232</v>
@@ -11081,7 +11081,7 @@
       <c r="J96" s="50"/>
       <c r="L96" s="122"/>
     </row>
-    <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7154</v>
@@ -11112,7 +11112,7 @@
       <c r="J97" s="50"/>
       <c r="L97" s="122"/>
     </row>
-    <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7238</v>
@@ -11143,7 +11143,7 @@
       <c r="J98" s="50"/>
       <c r="L98" s="122"/>
     </row>
-    <row r="99" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7237</v>
@@ -11174,7 +11174,7 @@
       <c r="J99" s="50"/>
       <c r="L99" s="122"/>
     </row>
-    <row r="100" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7241</v>
@@ -11205,7 +11205,7 @@
       <c r="J100" s="50"/>
       <c r="L100" s="122"/>
     </row>
-    <row r="101" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7332</v>
@@ -11236,7 +11236,7 @@
       <c r="J101" s="50"/>
       <c r="L101" s="122"/>
     </row>
-    <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="58" t="str">
         <f t="shared" si="11"/>
         <v>7333</v>
@@ -11267,7 +11267,7 @@
       <c r="J102" s="50"/>
       <c r="L102" s="122"/>
     </row>
-    <row r="103" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="145">
         <v>7608</v>
       </c>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="L103" s="122"/>
     </row>
-    <row r="104" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:67" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="145">
         <v>7610</v>
       </c>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="L104" s="122"/>
     </row>
-    <row r="105" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="48" t="s">
         <v>104</v>
       </c>
@@ -11404,7 +11404,7 @@
       <c r="BN105" s="122"/>
       <c r="BO105" s="122"/>
     </row>
-    <row r="106" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A106" s="58" t="str">
         <f t="shared" ref="A106:A135" si="15">RIGHT(D106,4)</f>
         <v>0614</v>
@@ -11491,7 +11491,7 @@
       <c r="BN106" s="122"/>
       <c r="BO106" s="122"/>
     </row>
-    <row r="107" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="58" t="str">
         <f t="shared" si="15"/>
         <v>3287</v>
@@ -11578,7 +11578,7 @@
       <c r="BN107" s="122"/>
       <c r="BO107" s="122"/>
     </row>
-    <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="58" t="str">
         <f t="shared" si="15"/>
         <v>5708</v>
@@ -11609,7 +11609,7 @@
       <c r="J108" s="29"/>
       <c r="L108" s="122"/>
     </row>
-    <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="58" t="str">
         <f t="shared" si="15"/>
         <v>4117</v>
@@ -11640,7 +11640,7 @@
       <c r="J109" s="29"/>
       <c r="L109" s="122"/>
     </row>
-    <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7316</v>
@@ -11671,7 +11671,7 @@
       <c r="J110" s="29"/>
       <c r="L110" s="122"/>
     </row>
-    <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7317</v>
@@ -11702,7 +11702,7 @@
       <c r="J111" s="29"/>
       <c r="L111" s="122"/>
     </row>
-    <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7143</v>
@@ -11733,7 +11733,7 @@
       <c r="J112" s="29"/>
       <c r="L112" s="122"/>
     </row>
-    <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7147</v>
@@ -11764,7 +11764,7 @@
       <c r="J113" s="29"/>
       <c r="L113" s="122"/>
     </row>
-    <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7456</v>
@@ -11795,7 +11795,7 @@
       <c r="J114" s="29"/>
       <c r="L114" s="122"/>
     </row>
-    <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7318</v>
@@ -11826,7 +11826,7 @@
       <c r="J115" s="29"/>
       <c r="L115" s="122"/>
     </row>
-    <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="58" t="str">
         <f t="shared" si="15"/>
         <v>3986</v>
@@ -11857,7 +11857,7 @@
       <c r="J116" s="29"/>
       <c r="L116" s="122"/>
     </row>
-    <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7364</v>
@@ -11888,7 +11888,7 @@
       <c r="J117" s="29"/>
       <c r="L117" s="122"/>
     </row>
-    <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7383</v>
@@ -11919,7 +11919,7 @@
       <c r="J118" s="29"/>
       <c r="L118" s="122"/>
     </row>
-    <row r="119" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="58" t="str">
         <f t="shared" si="15"/>
         <v>6967</v>
@@ -11950,7 +11950,7 @@
       <c r="J119" s="29"/>
       <c r="L119" s="122"/>
     </row>
-    <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="58" t="str">
         <f t="shared" si="15"/>
         <v>4993</v>
@@ -11981,7 +11981,7 @@
       <c r="J120" s="29"/>
       <c r="L120" s="122"/>
     </row>
-    <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="58" t="str">
         <f t="shared" si="15"/>
         <v>6937</v>
@@ -12012,7 +12012,7 @@
       <c r="J121" s="29"/>
       <c r="L121" s="122"/>
     </row>
-    <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="58" t="str">
         <f t="shared" si="15"/>
         <v>5483</v>
@@ -12043,7 +12043,7 @@
       <c r="J122" s="29"/>
       <c r="L122" s="122"/>
     </row>
-    <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="58" t="str">
         <f t="shared" si="15"/>
         <v>5931</v>
@@ -12074,7 +12074,7 @@
       <c r="J123" s="29"/>
       <c r="L123" s="122"/>
     </row>
-    <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="58" t="str">
         <f t="shared" si="15"/>
         <v>6832</v>
@@ -12105,7 +12105,7 @@
       <c r="J124" s="29"/>
       <c r="L124" s="122"/>
     </row>
-    <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7299</v>
@@ -12136,7 +12136,7 @@
       <c r="J125" s="29"/>
       <c r="L125" s="122"/>
     </row>
-    <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7386</v>
@@ -12167,7 +12167,7 @@
       <c r="J126" s="29"/>
       <c r="L126" s="122"/>
     </row>
-    <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="58" t="str">
         <f t="shared" si="15"/>
         <v>5679</v>
@@ -12198,7 +12198,7 @@
       <c r="J127" s="29"/>
       <c r="L127" s="122"/>
     </row>
-    <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="58" t="str">
         <f t="shared" si="15"/>
         <v>7382</v>
@@ -12229,7 +12229,7 @@
       <c r="J128" s="29"/>
       <c r="L128" s="122"/>
     </row>
-    <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="145">
         <v>7613</v>
       </c>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="L129" s="122"/>
     </row>
-    <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="145">
         <v>7616</v>
       </c>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="L130" s="122"/>
     </row>
-    <row r="131" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="58" t="str">
         <f t="shared" si="15"/>
         <v>6221</v>
@@ -12324,7 +12324,7 @@
       <c r="J131" s="29"/>
       <c r="L131" s="122"/>
     </row>
-    <row r="132" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="58" t="str">
         <f t="shared" si="15"/>
         <v>6222</v>
@@ -12355,7 +12355,7 @@
       <c r="J132" s="29"/>
       <c r="L132" s="122"/>
     </row>
-    <row r="133" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="147" t="str">
         <f t="shared" si="15"/>
         <v>6834</v>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="L133" s="122"/>
     </row>
-    <row r="134" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="58" t="str">
         <f t="shared" si="15"/>
         <v>6965</v>
@@ -12419,7 +12419,7 @@
       <c r="J134" s="29"/>
       <c r="L134" s="122"/>
     </row>
-    <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="58" t="str">
         <f t="shared" si="15"/>
         <v>6557</v>
@@ -12450,7 +12450,7 @@
       <c r="J135" s="29"/>
       <c r="L135" s="122"/>
     </row>
-    <row r="136" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="145">
         <v>7626</v>
       </c>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="L136" s="122"/>
     </row>
-    <row r="137" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="48" t="s">
         <v>104</v>
       </c>
@@ -12499,7 +12499,7 @@
       <c r="J137" s="44"/>
       <c r="L137" s="122"/>
     </row>
-    <row r="138" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:67" ht="16.149999999999999" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A138" s="58" t="str">
         <f t="shared" ref="A138:A147" si="20">RIGHT(D138,4)</f>
         <v>6470</v>
@@ -12530,7 +12530,7 @@
       <c r="J138" s="29"/>
       <c r="L138" s="122"/>
     </row>
-    <row r="139" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="58" t="str">
         <f t="shared" si="20"/>
         <v>6495</v>
@@ -12617,7 +12617,7 @@
       <c r="BN139" s="122"/>
       <c r="BO139" s="122"/>
     </row>
-    <row r="140" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="58" t="str">
         <f t="shared" si="20"/>
         <v>5452</v>
@@ -12704,7 +12704,7 @@
       <c r="BN140" s="122"/>
       <c r="BO140" s="122"/>
     </row>
-    <row r="141" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="58" t="str">
         <f t="shared" si="20"/>
         <v>6866</v>
@@ -12791,7 +12791,7 @@
       <c r="BN141" s="122"/>
       <c r="BO141" s="122"/>
     </row>
-    <row r="142" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="58" t="str">
         <f t="shared" si="20"/>
         <v>6025</v>
@@ -12878,7 +12878,7 @@
       <c r="BN142" s="122"/>
       <c r="BO142" s="122"/>
     </row>
-    <row r="143" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="58" t="str">
         <f t="shared" si="20"/>
         <v>4584</v>
@@ -12965,7 +12965,7 @@
       <c r="BN143" s="122"/>
       <c r="BO143" s="122"/>
     </row>
-    <row r="144" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="58" t="str">
         <f t="shared" si="20"/>
         <v>3215</v>
@@ -13052,7 +13052,7 @@
       <c r="BN144" s="122"/>
       <c r="BO144" s="122"/>
     </row>
-    <row r="145" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="58" t="str">
         <f t="shared" si="20"/>
         <v>5495</v>
@@ -13139,7 +13139,7 @@
       <c r="BN145" s="122"/>
       <c r="BO145" s="122"/>
     </row>
-    <row r="146" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="58" t="str">
         <f t="shared" si="20"/>
         <v>7377</v>
@@ -13226,7 +13226,7 @@
       <c r="BN146" s="122"/>
       <c r="BO146" s="122"/>
     </row>
-    <row r="147" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="58" t="str">
         <f t="shared" si="20"/>
         <v>6925</v>
@@ -13313,7 +13313,7 @@
       <c r="BN147" s="122"/>
       <c r="BO147" s="122"/>
     </row>
-    <row r="148" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="145">
         <v>7647</v>
       </c>
@@ -13401,7 +13401,7 @@
       <c r="BN148" s="122"/>
       <c r="BO148" s="122"/>
     </row>
-    <row r="149" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="145">
         <v>7651</v>
       </c>
@@ -13489,7 +13489,7 @@
       <c r="BN149" s="122"/>
       <c r="BO149" s="122"/>
     </row>
-    <row r="150" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="48" t="s">
         <v>104</v>
       </c>
@@ -13506,7 +13506,7 @@
       <c r="J150" s="44"/>
       <c r="L150" s="122"/>
     </row>
-    <row r="151" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A151" s="58" t="str">
         <f t="shared" ref="A151:A161" si="23">RIGHT(D151,4)</f>
         <v>6620</v>
@@ -13537,7 +13537,7 @@
       <c r="J151" s="29"/>
       <c r="L151" s="122"/>
     </row>
-    <row r="152" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="58" t="str">
         <f t="shared" si="23"/>
         <v>7187</v>
@@ -13568,7 +13568,7 @@
       <c r="J152" s="29"/>
       <c r="L152" s="122"/>
     </row>
-    <row r="153" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="145">
         <v>6008</v>
       </c>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="L153" s="122"/>
     </row>
-    <row r="154" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="58" t="str">
         <f t="shared" si="23"/>
         <v>7090</v>
@@ -13631,7 +13631,7 @@
       <c r="J154" s="29"/>
       <c r="L154" s="122"/>
     </row>
-    <row r="155" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="58" t="str">
         <f t="shared" si="23"/>
         <v>7103</v>
@@ -13662,7 +13662,7 @@
       <c r="J155" s="29"/>
       <c r="L155" s="122"/>
     </row>
-    <row r="156" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="58" t="str">
         <f>RIGHT(D156,4)</f>
         <v>6279</v>
@@ -13693,7 +13693,7 @@
       <c r="J156" s="29"/>
       <c r="L156" s="122"/>
     </row>
-    <row r="157" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="58" t="str">
         <f t="shared" si="23"/>
         <v>7092</v>
@@ -13724,7 +13724,7 @@
       <c r="J157" s="29"/>
       <c r="L157" s="122"/>
     </row>
-    <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="58" t="str">
         <f t="shared" si="23"/>
         <v>6448</v>
@@ -13755,7 +13755,7 @@
       <c r="J158" s="29"/>
       <c r="L158" s="122"/>
     </row>
-    <row r="159" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="58" t="str">
         <f t="shared" si="23"/>
         <v>6754</v>
@@ -13786,7 +13786,7 @@
       <c r="J159" s="29"/>
       <c r="L159" s="122"/>
     </row>
-    <row r="160" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="58" t="str">
         <f t="shared" si="23"/>
         <v>6208</v>
@@ -13817,7 +13817,7 @@
       <c r="J160" s="29"/>
       <c r="L160" s="122"/>
     </row>
-    <row r="161" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="58" t="str">
         <f t="shared" si="23"/>
         <v>6228</v>
@@ -13848,7 +13848,7 @@
       <c r="J161" s="29"/>
       <c r="L161" s="122"/>
     </row>
-    <row r="162" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="145">
         <v>7612</v>
       </c>
@@ -29144,7 +29144,13 @@
       <c r="J1687" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:J163" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J163" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
